--- a/Requisitos Funcionales (RF)/Requisitos Funcionales (RF) v 0.9/RF12_Contratos_v0.9.xlsx
+++ b/Requisitos Funcionales (RF)/Requisitos Funcionales (RF) v 0.9/RF12_Contratos_v0.9.xlsx
@@ -551,45 +551,38 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>El sistema debe permitir gestionar la información de contratos firmados con proveedores para el mantenimiento, soporte o servicios relacionados con uno o varios equipos médicos. Esto incluye el tipo de contrato, fechas de vigencia, costos, cobertura y condiciones específicas.</t>
+          <t>Gestionar contratos firmados con proveedores para mantenimiento, soporte o servicios de equipos médicos.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>- Registro de Nuevo Contrato
-- Consulta de Contratos (con filtros: proveedor, tipo, vigencia, equipo)
-- Edición de Información de Contrato
-- Eliminación de Contrato (con restricción: no eliminar si tiene OTs asociadas)
-- Asociación de Contrato a Equipos (N:M vía ContratoEquipo)
-- Asociación de Contrato a Proveedor (N:1)
-- Visualización en detalle de Equipo: tab "Contratos asociados"
-- Visualización en detalle de Proveedor: tab "Contratos"
-- Marca de OTs como "Cubiertas por Contrato" (campo contrato_id en OrdenTrabajo)
-- Cálculo de Costos Contractuales (acumulados por equipo/periodo) en reportes RF06
-- Badge visual: 🟢 Vigente / 🔴 Vencido / 🟡 Por vencer</t>
+          <t>- CRUD de contratos
+- Asociación a equipos (N:M vía ContratoEquipo)
+- Asociación a proveedor (N:1)
+- Visualización en detalle de Equipo y Proveedor
+- Marca de OTs como "Cubiertas por Contrato"
+- Cálculo de costos contractuales en reportes RF06
+- Badge: 🟢 Vigente / 🔴 Vencido / 🟡 Por vencer</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Contrato + ContratoEquipo (N:M)</t>
+          <t>Contrato + ContratoEquipo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>VER HOJA "Estructura_Tabla_Contrato" y "Estructura_Tabla_ContratoEquipo"</t>
+          <t>VER HOJAS "Estructura_Tabla_Contrato" y "Estructura_ContratoEquipo"</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>- RF01 (Activos): un equipo puede tener asociado uno o más contratos (N:M)
-- RF02 (OTs): las OTs pueden estar cubiertas por contrato (campo contrato_id opcional)
-- RF06 (Reportes): incluir costos contractuales en reportes, separando "cubiertos por contrato" vs "costos directos"
-- RF10 (Proveedores): un contrato se firma con un proveedor (N:1)</t>
+          <t>- RF01 (Activos), RF02 (OTs), RF06 (Reportes), RF10 (Proveedores)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Incorporar la gestión de contratos permite una visión financiera integral del mantenimiento de los equipos, diferenciando costos cubiertos por contrato de costos reales. Facilita la toma de decisiones sobre renovación de contratos, evaluación de proveedores y cálculo del costo total de propiedad (TCO) del equipo.</t>
+          <t>Visión financiera integral del mantenimiento. Diferencia costos cubiertos por contrato de costos reales.</t>
         </is>
       </c>
     </row>
@@ -634,12 +627,12 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Obligatorio (NOT NULL)</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Valor Predeterminado</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -679,7 +672,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Identificador único interno del sistema para el contrato.</t>
+          <t>Identificador único.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -714,7 +707,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ID del proveedor que firma el contrato (FK a `Proveedor.id`).</t>
+          <t>FK a Proveedor.id.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -749,12 +742,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tipo de contrato. Dropdown estricto (ver hoja "Valores_Enum").</t>
+          <t>Tipo de contrato. Dropdown estricto.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Enum: Comodato, Mantenimiento Preventivo, Mantenimiento Correctivo, Leasing, Garantía Extendida, Soporte Técnico, Servicio Integral, Otro</t>
+          <t>Ver hoja "Valores_Enum"</t>
         </is>
       </c>
     </row>
@@ -784,12 +777,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Fecha de inicio de vigencia del contrato.</t>
+          <t>Fecha de inicio de vigencia.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Se usa para calcular `activo`</t>
+          <t>Se usa para calcular activo</t>
         </is>
       </c>
     </row>
@@ -819,12 +812,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Fecha de fin de vigencia del contrato.</t>
+          <t>Fecha de fin de vigencia.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Se usa para calcular `activo`. Validación: fecha_fin &gt;= fecha_inicio</t>
+          <t>Validación: fecha_fin &gt;= fecha_inicio</t>
         </is>
       </c>
     </row>
@@ -854,12 +847,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Costo total del contrato (para contratos de pago único).</t>
+          <t>Costo total del contrato.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Si periodicidad_costo = "Único", usar este campo</t>
+          <t>Si periodicidad = Único</t>
         </is>
       </c>
     </row>
@@ -889,12 +882,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Costo periódico del contrato (mensual, trimestral, etc.).</t>
+          <t>Costo periódico.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Si periodicidad_costo != "Único", usar este campo</t>
+          <t>Si periodicidad != Único</t>
         </is>
       </c>
     </row>
@@ -924,12 +917,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Periodicidad del costo periódico. Dropdown estricto (ver hoja "Valores_Enum").</t>
+          <t>Periodicidad del costo.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Enum: Único, Mensual, Trimestral, Semestral, Anual</t>
+          <t>Ver hoja "Valores_Enum"</t>
         </is>
       </c>
     </row>
@@ -959,12 +952,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Moneda en la que se expresan los costos. Dropdown estricto (ver hoja "Valores_Enum").</t>
+          <t>Moneda de los costos.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Enum: USD, EUR, BOB, MXN, ARS, CLP, COP, PEN, BRL, Otro</t>
+          <t>Ver hoja "Valores_Enum"</t>
         </is>
       </c>
     </row>
@@ -994,7 +987,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Descripción detallada de lo que cubre el contrato.</t>
+          <t>Descripción de lo que cubre.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,12 +1022,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiempo máximo de respuesta del proveedor (ej. "24 hs", "48 hs").</t>
+          <t>Tiempo máximo de respuesta.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Texto libre</t>
+          <t>Ej: "24 hs"</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1057,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Horario de servicio acordado (ej. "Lun-Vie 8-18hs").</t>
+          <t>Horario de servicio.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Texto libre</t>
+          <t>Ej: "Lun-Vie 8-18hs"</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1092,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Notas o comentarios adicionales sobre el contrato.</t>
+          <t>Notas adicionales.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1134,12 +1127,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Fecha y hora en que se creó este registro en el sistema.</t>
+          <t>Fecha de creación en sistema.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Auditoría automática</t>
+          <t>Auditoría</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1146,7 @@
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>El estado `activo` (vigente/vencido) se CALCULA en runtime: `activo = fecha_inicio &lt;= hoy &lt;= fecha_fin`. No se almacena en la BD. En el schema Pydantic `ContratoRead` se agrega como campo computado. En el frontend se muestra con badge visual: 🟢 Vigente / 🔴 Vencido / 🟡 Por vencer (próximos 30 días).</t>
+          <t>El estado activo (vigente/vencido) se CALCULA en runtime: activo = fecha_inicio &lt;= hoy &lt;= fecha_fin. No se almacena. En el schema ContratoRead se agrega como campo computado. Badge visual: 🟢 Vigente / 🔴 Vencido / 🟡 Por vencer.</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1195,12 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Obligatorio (NOT NULL)</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Valor Predeterminado</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -1247,12 +1240,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ID del contrato (FK a `Contrato.id`).</t>
+          <t>FK a Contrato.id.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PK compuesta con equipo_id</t>
+          <t>PK compuesta</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1275,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ID del equipo (FK a `Equipo.id`).</t>
+          <t>FK a Equipo.id.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>PK compuesta con contrato_id</t>
+          <t>PK compuesta</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1294,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Se descartó la opción de `grupo_equipos` como TEXT serializado ('1,5,7,12') porque rompe las relaciones FK, hace queries frágiles (LIKE %X%), no soporta cascade al eliminar, y dificulta contar cuántos equipos cubre un contrato. La tabla intermedia `ContratoEquipo` es el estándar para relaciones N:M en bases relacionales: FKs correctas, JOIN eficiente, cascade automático, queries simples.</t>
+          <t>Se descartó grupo_equipos como TEXT serializado porque rompe FKs, hace queries frágiles (LIKE), no soporta cascade, y dificulta contar equipos. La tabla intermedia ContratoEquipo es estándar para N:M: FKs correctas, JOIN eficiente, cascade automático.</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1360,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Préstamo gratuito de equipo por tiempo determinado</t>
+          <t>Préstamo gratuito de equipo</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1420,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Arrendamiento financiero del equipo</t>
+          <t>Arrendamiento financiero</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1460,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Asistencia técnica remota o presencial</t>
+          <t>Asistencia técnica</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1550,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Pago mensual (usar costo_periodico)</t>
+          <t>Pago mensual</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1820,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Otra moneda no listada</t>
+          <t>Otra moneda</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1888,12 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Flag `genera_mp_automatico: bool` en Contrato. Si es True y tipo_contrato = "Mantenimiento Preventivo", genera tareas MP automáticamente según frecuencia definida en el contrato.</t>
+          <t>Flag genera_mp_automatico. Si True y tipo=MP, genera tareas MP según frecuencia.</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Útil para contratos de servicio integral. El contrato define la frecuencia y el sistema crea las MPs sin intervención manual.</t>
+          <t>Útil para contratos de servicio integral.</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1913,12 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Flag `renovacion_automatica: bool`. Si es True, al vencerse el contrato, se crea uno nuevo automáticamente con mismas condiciones pero nuevas fechas.</t>
+          <t>Flag renovacion_automatica. Al vencer, crea contrato nuevo con mismas condiciones.</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Útil para contratos de servicio continuo. Requiere confirmación del administrador.</t>
+          <t>Requiere confirmación del administrador.</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1938,12 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>En el dashboard, mostrar "X contratos por vencer en los próximos 30/60/90 días".</t>
+          <t>Dashboard: "X contratos por vencer en 30/60/90 días".</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Útil para planificación financiera. Fácil de implementar una vez que Contrato exista.</t>
+          <t>Planificación financiera.</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1963,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Subir el PDF del contrato firmado usando DocumentoAdjunto con categoria="contrato" y contrato_id.</t>
+          <t>Subir PDF del contrato firmado usando DocumentoAdjunto con categoria="contrato".</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Reutiliza infraestructura existente. Permite tener el contrato físico escaneado disponible en el sistema.</t>
+          <t>Reutiliza infraestructura existente.</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1988,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Tabla `ContratoHistorial` que registre cambios (fechas, costos, cobertura) con auditoría.</t>
+          <t>Tabla ContratoHistorial con auditoría de cambios.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Para trazabilidad de modificaciones contractuales. Útil para disputas legales.</t>
+          <t>Trazabilidad de modificaciones.</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2013,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Exportar costos contractuales a formato contable para importar en sistema contable del hospital.</t>
+          <t>Exportar costos contractuales a formato contable.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Similar a RF11 opción futura. Requiere coordinación con sistema contable específico.</t>
+          <t>Requiere coordinación con sistema contable.</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2038,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Sistema de scoring de proveedores basado en cumplimiento de contratos (tiempo de respuesta, OTs cerradas a tiempo, etc.).</t>
+          <t>Sistema de scoring basado en cumplimiento de contratos.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Permite comparar proveedores objetivamente. Útil para decisiones de renovación.</t>
+          <t>Comparar proveedores objetivamente.</t>
         </is>
       </c>
     </row>
